--- a/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{782F4F85-AAED-4200-A93A-65A8ED73DC81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C64175F-6A2D-4AC5-9C73-5307551DF7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="21600" windowHeight="12683" xr2:uid="{EDB7D1CB-C89A-41CC-AD32-0A9154075ED3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A0C9EBA5-2CE4-4F05-9277-577A1B0E4731}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -781,7 +781,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{287F4BB7-E9F0-4D1D-BE2A-DC960DFDEEC7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A7B647-F350-484C-AF2A-A9D69B59F0CE}">
   <dimension ref="B3:L40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C64175F-6A2D-4AC5-9C73-5307551DF7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1551D73D-0F4E-440D-9BAA-C2CE0746BB65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{A0C9EBA5-2CE4-4F05-9277-577A1B0E4731}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CF9B97CC-FFA2-4CEC-B6DE-BF73BE55A605}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -781,7 +781,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23A7B647-F350-484C-AF2A-A9D69B59F0CE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FA0AC0-68B6-4536-8202-E198035CB72D}">
   <dimension ref="B3:L40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1551D73D-0F4E-440D-9BAA-C2CE0746BB65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A58683A-6077-465C-B254-6D75CFAE2524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{CF9B97CC-FFA2-4CEC-B6DE-BF73BE55A605}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5B527879-BB56-489C-B666-699B97FB8A82}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -781,7 +781,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20FA0AC0-68B6-4536-8202-E198035CB72D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E5580D3-BCF1-4DF4-91D3-3BC4B10C12F9}">
   <dimension ref="B3:L40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A58683A-6077-465C-B254-6D75CFAE2524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AA3FA30-91FF-4CC1-8EEA-BB1FD6F62D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5B527879-BB56-489C-B666-699B97FB8A82}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{284E36B9-BF9C-4A4E-8A09-5F4B6A4FF254}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -781,7 +781,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E5580D3-BCF1-4DF4-91D3-3BC4B10C12F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBF115C4-6E02-4CB8-B285-47F08B334845}">
   <dimension ref="B3:L40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AA3FA30-91FF-4CC1-8EEA-BB1FD6F62D87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E559675C-96CD-4FA4-AF07-DC4FFAB23B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{284E36B9-BF9C-4A4E-8A09-5F4B6A4FF254}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FD5B049D-6893-4DD2-A459-D9CCD2026618}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -781,7 +781,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBF115C4-6E02-4CB8-B285-47F08B334845}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D8512AC-B7F9-4026-BA77-3561B25604F5}">
   <dimension ref="B3:L40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E559675C-96CD-4FA4-AF07-DC4FFAB23B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{537C843E-68A9-4694-A11B-A52F5A4947C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{FD5B049D-6893-4DD2-A459-D9CCD2026618}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E81222FB-B797-4F36-B069-3612015C0191}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -781,7 +781,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D8512AC-B7F9-4026-BA77-3561B25604F5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF1BF676-9B17-46D5-A55E-D4773076AF36}">
   <dimension ref="B3:L40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{537C843E-68A9-4694-A11B-A52F5A4947C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{23EAB962-25CB-437D-AB49-F86129A6833F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E81222FB-B797-4F36-B069-3612015C0191}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B4749789-CF6B-4182-8871-1B8E4E43CB98}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -781,7 +781,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF1BF676-9B17-46D5-A55E-D4773076AF36}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8897EBCB-3409-4377-B896-BC2820BA3499}">
   <dimension ref="B3:L40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23EAB962-25CB-437D-AB49-F86129A6833F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAB9DDD3-DBD6-4C22-B938-085E37D0D678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{B4749789-CF6B-4182-8871-1B8E4E43CB98}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{21F9FFFB-777F-44A9-8098-C0D5E5109D6E}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -781,7 +781,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8897EBCB-3409-4377-B896-BC2820BA3499}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{442D531D-7C95-4EF9-885F-60C031546E02}">
   <dimension ref="B3:L40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAB9DDD3-DBD6-4C22-B938-085E37D0D678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{81F7993F-899A-4B3C-A892-78529AB71796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{21F9FFFB-777F-44A9-8098-C0D5E5109D6E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{286B449B-FEFE-47A1-A351-2B016AE915CF}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -781,7 +781,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{442D531D-7C95-4EF9-885F-60C031546E02}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45AD534A-D9E1-4CD9-BA0F-D57685722E8B}">
   <dimension ref="B3:L40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
+++ b/VerveStacks_KEN_grids_kan/SuppXLS/trades/scentrade__trade_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan\SuppXLS\trades\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{81F7993F-899A-4B3C-A892-78529AB71796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{18B46E00-162B-4268-878E-57579648962C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{286B449B-FEFE-47A1-A351-2B016AE915CF}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{57388D27-0720-49F1-9D45-2F1AEF5E5069}"/>
   </bookViews>
   <sheets>
     <sheet name="grid_links" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,9 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -68,232 +71,232 @@
     <t>ELC</t>
   </si>
   <si>
-    <t>e_KE13-400</t>
-  </si>
-  <si>
-    <t>e_w870818913-400</t>
-  </si>
-  <si>
-    <t>g_KE13-400-w870818913-400</t>
+    <t>e_KE13-400_KEN</t>
+  </si>
+  <si>
+    <t>e_w870818913-400_KEN</t>
+  </si>
+  <si>
+    <t>g_KE13-400_KEN-w870818913-400_KEN</t>
   </si>
   <si>
     <t>B</t>
   </si>
   <si>
-    <t>e_KE14-400</t>
-  </si>
-  <si>
-    <t>e_w578140339-400</t>
-  </si>
-  <si>
-    <t>g_KE14-400-w578140339-400</t>
-  </si>
-  <si>
-    <t>e_KE15-220</t>
-  </si>
-  <si>
-    <t>e_w953567827-220</t>
-  </si>
-  <si>
-    <t>g_KE15-220-w953567827-220</t>
-  </si>
-  <si>
-    <t>e_KE2-220</t>
-  </si>
-  <si>
-    <t>e_KE3-220</t>
-  </si>
-  <si>
-    <t>g_KE2-220-KE3-220</t>
-  </si>
-  <si>
-    <t>e_KE4-220</t>
-  </si>
-  <si>
-    <t>e_KE5-220</t>
-  </si>
-  <si>
-    <t>g_KE4-220-KE5-220</t>
-  </si>
-  <si>
-    <t>e_KE7-220</t>
-  </si>
-  <si>
-    <t>e_w457973270-220</t>
-  </si>
-  <si>
-    <t>g_KE7-220-w457973270-220</t>
-  </si>
-  <si>
-    <t>e_KE8-220</t>
-  </si>
-  <si>
-    <t>e_w569997185-220</t>
-  </si>
-  <si>
-    <t>g_KE8-220-w569997185-220</t>
-  </si>
-  <si>
-    <t>e_KE9-220</t>
-  </si>
-  <si>
-    <t>e_w86402221-220</t>
-  </si>
-  <si>
-    <t>g_KE9-220-w86402221-220</t>
-  </si>
-  <si>
-    <t>e_r14923640-220</t>
-  </si>
-  <si>
-    <t>e_w579310367-220</t>
-  </si>
-  <si>
-    <t>g_r14923640-220-w579310367-220</t>
-  </si>
-  <si>
-    <t>e_r14923640-400</t>
-  </si>
-  <si>
-    <t>e_w457973270-400</t>
-  </si>
-  <si>
-    <t>g_r14923640-400-w457973270-400</t>
-  </si>
-  <si>
-    <t>e_w1115312336-220</t>
-  </si>
-  <si>
-    <t>g_w1115312336-220-r14923640-220</t>
-  </si>
-  <si>
-    <t>e_w180021151-220</t>
-  </si>
-  <si>
-    <t>g_w180021151-220-KE9-220</t>
-  </si>
-  <si>
-    <t>e_w220540545-220</t>
-  </si>
-  <si>
-    <t>e_KE6-220</t>
-  </si>
-  <si>
-    <t>g_w220540545-220-KE6-220</t>
-  </si>
-  <si>
-    <t>e_w669520367-220</t>
-  </si>
-  <si>
-    <t>g_w220540545-220-w669520367-220</t>
-  </si>
-  <si>
-    <t>g_w220540545-220-w86402221-220</t>
-  </si>
-  <si>
-    <t>g_w457973270-220-KE8-220</t>
-  </si>
-  <si>
-    <t>g_w457973270-220-w569997185-220</t>
-  </si>
-  <si>
-    <t>g_w569997185-220-w180021151-220</t>
-  </si>
-  <si>
-    <t>e_w669510376-220</t>
-  </si>
-  <si>
-    <t>g_w569997185-220-w669510376-220</t>
-  </si>
-  <si>
-    <t>e_w569997185-400</t>
-  </si>
-  <si>
-    <t>e_w563813243-400</t>
-  </si>
-  <si>
-    <t>g_w569997185-400-w563813243-400</t>
-  </si>
-  <si>
-    <t>g_w569997185-400-w578140339-400</t>
-  </si>
-  <si>
-    <t>e_w578140339-220</t>
-  </si>
-  <si>
-    <t>e_KE11-220</t>
-  </si>
-  <si>
-    <t>g_w578140339-220-KE11-220</t>
-  </si>
-  <si>
-    <t>e_KE12-400</t>
-  </si>
-  <si>
-    <t>g_w578140339-400-KE12-400</t>
-  </si>
-  <si>
-    <t>g_w578140339-400-KE13-400</t>
-  </si>
-  <si>
-    <t>e_KE1-220</t>
-  </si>
-  <si>
-    <t>g_w579310367-220-KE1-220</t>
-  </si>
-  <si>
-    <t>e_w659874569-220</t>
-  </si>
-  <si>
-    <t>e_w660091166-220</t>
-  </si>
-  <si>
-    <t>g_w659874569-220-w660091166-220</t>
-  </si>
-  <si>
-    <t>e_w665372427-220</t>
-  </si>
-  <si>
-    <t>e_KE10-220</t>
-  </si>
-  <si>
-    <t>g_w665372427-220-KE10-220</t>
-  </si>
-  <si>
-    <t>g_w665372427-220-KE11-220</t>
-  </si>
-  <si>
-    <t>g_w669520367-220-KE15-220</t>
-  </si>
-  <si>
-    <t>g_w669520367-220-w86402221-220</t>
-  </si>
-  <si>
-    <t>e_w696445754-220</t>
-  </si>
-  <si>
-    <t>g_w696445754-220-KE1-220</t>
-  </si>
-  <si>
-    <t>e_w846713577-220</t>
-  </si>
-  <si>
-    <t>g_w846713577-220-w669510376-220</t>
-  </si>
-  <si>
-    <t>g_w86402221-220-KE10-220</t>
-  </si>
-  <si>
-    <t>g_w86402221-220-w220540545-220</t>
-  </si>
-  <si>
-    <t>e_w870818913-220</t>
-  </si>
-  <si>
-    <t>g_w870818913-220-KE15-220</t>
-  </si>
-  <si>
-    <t>g_w953567827-220-w659874569-220</t>
+    <t>e_KE14-400_KEN</t>
+  </si>
+  <si>
+    <t>e_w578140339-400_KEN</t>
+  </si>
+  <si>
+    <t>g_KE14-400_KEN-w578140339-400_KEN</t>
+  </si>
+  <si>
+    <t>e_KE15-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w953567827-220_KEN</t>
+  </si>
+  <si>
+    <t>g_KE15-220_KEN-w953567827-220_KEN</t>
+  </si>
+  <si>
+    <t>e_KE2-220_KEN</t>
+  </si>
+  <si>
+    <t>e_KE3-220_KEN</t>
+  </si>
+  <si>
+    <t>g_KE2-220_KEN-KE3-220_KEN</t>
+  </si>
+  <si>
+    <t>e_KE4-220_KEN</t>
+  </si>
+  <si>
+    <t>e_KE5-220_KEN</t>
+  </si>
+  <si>
+    <t>g_KE4-220_KEN-KE5-220_KEN</t>
+  </si>
+  <si>
+    <t>e_KE7-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w457973270-220_KEN</t>
+  </si>
+  <si>
+    <t>g_KE7-220_KEN-w457973270-220_KEN</t>
+  </si>
+  <si>
+    <t>e_KE8-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w569997185-220_KEN</t>
+  </si>
+  <si>
+    <t>g_KE8-220_KEN-w569997185-220_KEN</t>
+  </si>
+  <si>
+    <t>e_KE9-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w86402221-220_KEN</t>
+  </si>
+  <si>
+    <t>g_KE9-220_KEN-w86402221-220_KEN</t>
+  </si>
+  <si>
+    <t>e_r14923640-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w579310367-220_KEN</t>
+  </si>
+  <si>
+    <t>g_r14923640-220_KEN-w579310367-220_KEN</t>
+  </si>
+  <si>
+    <t>e_r14923640-400_KEN</t>
+  </si>
+  <si>
+    <t>e_w457973270-400_KEN</t>
+  </si>
+  <si>
+    <t>g_r14923640-400_KEN-w457973270-400_KEN</t>
+  </si>
+  <si>
+    <t>e_w1115312336-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w1115312336-220_KEN-r14923640-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w180021151-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w180021151-220_KEN-KE9-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w220540545-220_KEN</t>
+  </si>
+  <si>
+    <t>e_KE6-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w220540545-220_KEN-KE6-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w669520367-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w220540545-220_KEN-w669520367-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w220540545-220_KEN-w86402221-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w457973270-220_KEN-KE8-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w457973270-220_KEN-w569997185-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w569997185-220_KEN-w180021151-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w669510376-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w569997185-220_KEN-w669510376-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w569997185-400_KEN</t>
+  </si>
+  <si>
+    <t>e_w563813243-400_KEN</t>
+  </si>
+  <si>
+    <t>g_w569997185-400_KEN-w563813243-400_KEN</t>
+  </si>
+  <si>
+    <t>g_w569997185-400_KEN-w578140339-400_KEN</t>
+  </si>
+  <si>
+    <t>e_w578140339-220_KEN</t>
+  </si>
+  <si>
+    <t>e_KE11-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w578140339-220_KEN-KE11-220_KEN</t>
+  </si>
+  <si>
+    <t>e_KE12-400_KEN</t>
+  </si>
+  <si>
+    <t>g_w578140339-400_KEN-KE12-400_KEN</t>
+  </si>
+  <si>
+    <t>g_w578140339-400_KEN-KE13-400_KEN</t>
+  </si>
+  <si>
+    <t>e_KE1-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w579310367-220_KEN-KE1-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w659874569-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w660091166-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w659874569-220_KEN-w660091166-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w665372427-220_KEN</t>
+  </si>
+  <si>
+    <t>e_KE10-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w665372427-220_KEN-KE10-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w665372427-220_KEN-KE11-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w669520367-220_KEN-KE15-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w669520367-220_KEN-w86402221-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w696445754-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w696445754-220_KEN-KE1-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w846713577-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w846713577-220_KEN-w669510376-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w86402221-220_KEN-KE10-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w86402221-220_KEN-w220540545-220_KEN</t>
+  </si>
+  <si>
+    <t>e_w870818913-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w870818913-220_KEN-KE15-220_KEN</t>
+  </si>
+  <si>
+    <t>g_w953567827-220_KEN-w659874569-220_KEN</t>
   </si>
   <si>
     <t>~tradelinks_desc</t>
@@ -781,7 +784,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45AD534A-D9E1-4CD9-BA0F-D57685722E8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0234A43-5A90-47D0-9250-A319B2F42EDD}">
   <dimension ref="B3:L40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
